--- a/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_acikgozOverviewCurrencyUsefulness2022.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_acikgozOverviewCurrencyUsefulness2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C345189C-6F14-894D-98A0-0A3791817893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A68239-5023-8445-A0A4-403CFD77A550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="41580" yWindow="1700" windowWidth="27640" windowHeight="16940" xr2:uid="{FAE372B2-FC2A-7448-8E9F-1C36772B81B4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="64">
   <si>
     <t>Test Name</t>
   </si>
@@ -209,9 +209,6 @@
     <t>Total duration of immobility during test session</t>
   </si>
   <si>
-    <t>Depression-like behavior (behavioral despair)</t>
-  </si>
-  <si>
     <t>Tail suspension test</t>
   </si>
   <si>
@@ -227,14 +224,17 @@
     <t>Anhedonia</t>
   </si>
   <si>
-    <t>Depression‐like behavior</t>
+    <t>Depression-like behavior</t>
+  </si>
+  <si>
+    <t>Behavioral</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -248,6 +248,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -271,9 +277,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -612,8 +619,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="45.6640625" customWidth="1"/>
-    <col min="2" max="2" width="78.33203125" customWidth="1"/>
-    <col min="3" max="3" width="35.6640625" customWidth="1"/>
+    <col min="2" max="2" width="105.83203125" customWidth="1"/>
+    <col min="3" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -631,280 +638,298 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B15" t="s">
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B16" t="s">
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B17" t="s">
         <v>44</v>
       </c>
       <c r="C17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B18" t="s">
         <v>46</v>
       </c>
+      <c r="C18" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B19" t="s">
         <v>46</v>
       </c>
       <c r="C19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B20" t="s">
         <v>48</v>
       </c>
       <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B21" t="s">
         <v>50</v>
       </c>
       <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B22" t="s">
         <v>52</v>
       </c>
       <c r="C22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B23" t="s">
@@ -914,35 +939,35 @@
         <v>63</v>
       </c>
       <c r="D23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
+      <c r="B24" t="s">
         <v>58</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C24" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+      <c r="B25" t="s">
         <v>60</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" t="s">
         <v>61</v>
-      </c>
-      <c r="C25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_acikgozOverviewCurrencyUsefulness2022.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_acikgozOverviewCurrencyUsefulness2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A68239-5023-8445-A0A4-403CFD77A550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEB88AD-4D2F-464D-AD02-BED32C7B3227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41580" yWindow="1700" windowWidth="27640" windowHeight="16940" xr2:uid="{FAE372B2-FC2A-7448-8E9F-1C36772B81B4}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{FAE372B2-FC2A-7448-8E9F-1C36772B81B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
